--- a/perf_study/plot/overall_perf_study.xlsx
+++ b/perf_study/plot/overall_perf_study.xlsx
@@ -436,17 +436,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>IPC gain (geomain)</t>
+          <t>IPC (geomean)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>GLOBAL_ACC_R fails (geomain)</t>
+          <t>GLOBAL_ACC_R fails (geomean)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>GLOBAL_ACC_W fails (geomain)</t>
+          <t>GLOBAL_ACC_W fails (geomean)</t>
         </is>
       </c>
     </row>
@@ -456,14 +456,20 @@
           <t>base-config</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>0</v>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>60.960</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>1950.799</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>44.344</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -472,14 +478,20 @@
           <t>mshr-entries-32</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>4.895</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>-96.01300000000001</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>-99.754</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>60.995 (+0.057%)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>439.309 (-77.481%)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>7.473 (-83.148%)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/perf_study/plot/overall_perf_study.xlsx
+++ b/perf_study/plot/overall_perf_study.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,11 @@
         <fgColor rgb="FFD4F5D4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D0D0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -56,10 +61,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,17 +442,37 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>IPC (geomean)</t>
+          <t>IPC</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>GLOBAL_ACC_R fails (geomean)</t>
+          <t>L2_BW</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>GLOBAL_ACC_W fails (geomean)</t>
+          <t>L2_total_cache_accesses</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>L2_GLOBAL_ACC_W_TOTAL_ACCESS</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>MISS_QUEUE_FULL</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MSHR_ENTRY_FAIL</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>MSHR_MERGE_ENTRY_FAIL</t>
         </is>
       </c>
     </row>
@@ -463,34 +489,704 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1950.799</t>
+          <t>15.843</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>44.344</t>
+          <t>14553.780</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>3671.740</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>1476.818</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>12.146</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mshr-entries-32</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>60.995 (+0.057%)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>439.309 (-77.481%)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>7.473 (-83.148%)</t>
+          <t>default-cfg-11-25-eve</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>60.960 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>15.843 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>14553.780 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>3671.740 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>1476.818 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>0.000 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>12.146 (+0.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>miss-q-ent-32-and-mshr-max-merge-32</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>61.149 (+0.310%)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>15.892 (+0.310%)</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>14553.780 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>3671.740 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>307.096 (-79.206%)</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>0.000 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>miss-q-ent-64-and-mshr-max-merge-32</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>61.237 (+0.455%)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>15.915 (+0.455%)</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>14553.780 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>3671.740 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18.689 (-98.734%)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>0.845 (+inf%)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>miss-q-ent-128-and-mshr-max-merge-32</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>61.227 (+0.439%)</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>15.913 (+0.439%)</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>14553.780 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>3671.740 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2.198 (-99.851%)</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>1.158 (+inf%)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>miss-q-ent-256-and-mshr-max-merge-32</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>61.234 (+0.450%)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>15.914 (+0.450%)</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>14553.780 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>3671.740 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2.500 (-99.831%)</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2.137 (+inf%)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>miss-q-ent-288-and-mshr-max-merge-32</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>61.232 (+0.446%)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>15.914 (+0.446%)</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>14553.780 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>3671.740 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2.392 (-99.838%)</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>2.367 (+inf%)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>miss-q-ent-320-and-mshr-max-merge-32</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>61.230 (+0.443%)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>15.913 (+0.443%)</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>14553.780 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>3671.740 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2.221 (-99.850%)</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2.524 (+inf%)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>miss-q-ent-352-and-mshr-max-merge-32</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>61.240 (+0.459%)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>15.916 (+0.459%)</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>14553.780 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>3671.740 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1.238 (-99.916%)</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>2.677 (+inf%)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>miss-q-ent-384-and-mshr-max-merge-32</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>61.236 (+0.453%)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>15.915 (+0.453%)</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>14553.780 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>3671.740 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>2.683 (+inf%)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>miss-q-ent-512-and-mshr-max-merge-32</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>61.236 (+0.453%)</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>15.915 (+0.453%)</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>14553.780 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>3671.740 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>2.683 (+inf%)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>gpgpusim-iter-II-mshr-entries-1024</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>61.238 (+0.457%)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>15.915 (+0.457%)</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>14553.780 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>3671.740 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2.449 (-99.834%)</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>0.000 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dse-iter-II-mshr-ent-1024-mq-ent-wp-wb</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>62.294 (+2.189%)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9.831 (-37.949%)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9094.376 (-37.512%)</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2.448 (-99.834%)</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>0.000 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dse-iter-II-mshr-ent-1024-miss-q-ent-512-mq-ent-wp-wb</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>62.296 (+2.191%)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>9.831 (-37.948%)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9094.376 (-37.512%)</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2.150 (-99.854%)</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>0.000 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dse-iter-II-mshr-ent-1024-miss-q-ent-1024-mq-ent-wp-wb</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>62.302 (+2.202%)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>9.832 (-37.942%)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9094.376 (-37.512%)</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>0.000 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dse-iter-II-mshr-ent-1024-miss-q-ent-768-mq-ent-wp-wb</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>62.302 (+2.202%)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9.832 (-37.942%)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9094.376 (-37.512%)</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>0.000 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dse-iter-II-mshr-ent-1024-miss-q-ent-640-mq-ent-wp-wb</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>62.302 (+2.202%)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>9.832 (-37.941%)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9094.376 (-37.512%)</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0.194 (-99.987%)</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>0.000 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0.000 (-100.000%)</t>
         </is>
       </c>
     </row>

--- a/perf_study/plot/overall_perf_study.xlsx
+++ b/perf_study/plot/overall_perf_study.xlsx
@@ -40,12 +40,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D0D0"/>
+        <fgColor rgb="FFD4F5D4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4F5D4"/>
+        <fgColor rgb="FFF8D0D0"/>
       </patternFill>
     </fill>
   </fills>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,16 @@
           <t>MSHR_MERGE_ENTRY_FAIL</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>MSHR_ENTRY_FAIL</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>LINE_ALLOC_FAIL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,106 +489,136 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>60.960</t>
+          <t>29.871</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>15.843</t>
+          <t>5.756</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>14553.780</t>
+          <t>12066.066</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>3671.740</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>1476.818</t>
+          <t>13170.246</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>12.146</t>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>0.864</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>default-cfg-11-25-eve</t>
+          <t>regress_disable_mshr_l2_correlation</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>60.960 (+0.000%)</t>
+          <t>29.871 (+0.000%)</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>15.843 (+0.000%)</t>
+          <t>5.756 (+0.000%)</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>14553.780 (+0.000%)</t>
+          <t>12066.066 (+0.000%)</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>3671.740 (+0.000%)</t>
+          <t>0.000 (+0.000%)</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>1476.818 (+0.000%)</t>
+          <t>13170.246 (+0.000%)</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>12.146 (+0.000%)</t>
+          <t>0.000 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>0.000 (+0.000%)</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>0.864 (+0.000%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l2_max_merge_zero</t>
+          <t>regress_enable_mshr_l2_correlation</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>60.342 (-1.013%)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>15.683 (-1.013%)</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>14553.780 (+0.000%)</t>
+          <t>34.293 (+14.801%)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4.628 (-19.594%)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8536.831 (-29.249%)</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>3671.740 (+0.000%)</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1810.607 (+22.602%)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13.647 (+12.356%)</t>
+          <t>3577.276 (-72.838%)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>146.261 (+inf%)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>7.180 (+inf%)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>1.647 (+90.605%)</t>
         </is>
       </c>
     </row>
